--- a/numerical-workflows/v2/framework/04_数值文档/经济/经济知识工具页_镜像.xlsx
+++ b/numerical-workflows/v2/framework/04_数值文档/经济/经济知识工具页_镜像.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="943" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="道具定价" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="角色、专武、旅券掉落池" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="讨论页-玩法定位和产出" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具定价" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色、专武、旅券掉落池" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨论页-玩法定位和产出" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
